--- a/output/graficos_nacionales/plot_nacional_piramides_regiones_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_piramides_regiones_2022.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 00:53</t>
+    <t xml:space="preserve">2026-10-05 21:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
